--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\Thông báo Phạt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA19D56B-F02B-4372-86AA-61503D5FD652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F7E9B7-E7D7-4D5E-86D0-4786B28397DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73357F53-6859-4A3C-831D-A4EDAE5BC3C5}"/>
   </bookViews>
@@ -57,15 +57,9 @@
     <t>Địa Chỉ</t>
   </si>
   <si>
-    <t>5990201015708</t>
-  </si>
-  <si>
     <t>CTY CO PHAN CHAN NUOI C.P VIET NAM</t>
   </si>
   <si>
-    <t>Agribank</t>
-  </si>
-  <si>
     <t>Nội Dung Chuyển Khoản</t>
   </si>
   <si>
@@ -280,6 +274,12 @@
   </si>
   <si>
     <t>BP0016 510229000 VN07 Nop Phat Heo Chet</t>
+  </si>
+  <si>
+    <t>Sacombank</t>
+  </si>
+  <si>
+    <t>050064616177</t>
   </si>
 </sst>
 </file>
@@ -323,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -331,6 +331,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +402,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2396AF4C-3A31-4DDF-8AD3-059920292CCC}" name="Table2" displayName="Table2" ref="A1:I4" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2396AF4C-3A31-4DDF-8AD3-059920292CCC}" name="Table2" displayName="Table2" ref="A1:I4" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:I4" xr:uid="{2396AF4C-3A31-4DDF-8AD3-059920292CCC}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3F81DF6B-7901-4ED5-A39F-EE8426A11EB4}" name="Tên Lò Giết Mổ"/>
@@ -419,7 +420,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52BDD1F3-4FC7-4472-B014-BE00547F56D3}" name="Table1" displayName="Table1" ref="A1:F17" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52BDD1F3-4FC7-4472-B014-BE00547F56D3}" name="Table1" displayName="Table1" ref="A1:F17" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:F17" xr:uid="{52BDD1F3-4FC7-4472-B014-BE00547F56D3}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E03370C3-903C-4184-876F-E292C425E36E}" name="Số Xe"/>
@@ -766,31 +767,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -801,25 +802,25 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -830,25 +831,25 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -859,25 +860,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" t="s">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
-        <v>6</v>
-      </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -904,39 +905,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4">
         <v>46023</v>
@@ -944,19 +945,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4">
         <v>46023</v>
@@ -964,19 +965,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="4">
         <v>46023</v>
@@ -984,19 +985,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4">
         <v>46204</v>
@@ -1004,19 +1005,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="4">
         <v>46204</v>
@@ -1024,19 +1025,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4">
         <v>46023</v>
@@ -1044,19 +1045,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="4">
         <v>46268</v>
@@ -1064,19 +1065,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4">
         <v>46136</v>
@@ -1084,19 +1085,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F10" s="4">
         <v>46023</v>
@@ -1104,19 +1105,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="4">
         <v>46023</v>
@@ -1124,19 +1125,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" s="4">
         <v>46023</v>
@@ -1144,19 +1145,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4">
         <v>46204</v>
@@ -1164,19 +1165,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14" s="4">
         <v>46204</v>
@@ -1184,19 +1185,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F15" s="4">
         <v>46023</v>
@@ -1204,19 +1205,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" s="4">
         <v>46023</v>
@@ -1224,19 +1225,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="4">
         <v>46023</v>

--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\Thông báo Phạt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F7E9B7-E7D7-4D5E-86D0-4786B28397DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0044B99B-AAF6-485B-A831-8DC5B6D87913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73357F53-6859-4A3C-831D-A4EDAE5BC3C5}"/>
   </bookViews>
@@ -276,10 +276,10 @@
     <t>BP0016 510229000 VN07 Nop Phat Heo Chet</t>
   </si>
   <si>
-    <t>Sacombank</t>
-  </si>
-  <si>
-    <t>050064616177</t>
+    <t>Vietcombank</t>
+  </si>
+  <si>
+    <t>0121000090194</t>
   </si>
 </sst>
 </file>
